--- a/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-(IED)-PRUEBA-502__CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-(IED)-PRUEBA-502__CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-(IED)-PRUEBA-502__CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-(IED)-PRUEBA-502__CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1803,11 +1787,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1815,7 +1795,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2056,11 +2036,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2068,7 +2044,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2309,11 +2285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2321,7 +2293,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2562,11 +2534,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2574,7 +2542,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2811,11 +2779,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2823,7 +2787,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3056,11 +3020,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3068,7 +3028,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3309,11 +3269,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3321,7 +3277,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3562,11 +3518,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3574,7 +3526,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3811,11 +3763,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3823,7 +3771,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4056,11 +4004,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4068,7 +4012,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4309,11 +4253,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4321,7 +4261,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4558,11 +4498,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4570,7 +4506,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4811,11 +4747,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4823,7 +4755,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5064,11 +4996,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5076,7 +5004,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5317,11 +5245,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5329,7 +5253,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5566,11 +5490,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5578,7 +5498,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5819,11 +5739,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5831,7 +5747,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6060,11 +5976,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6072,7 +5984,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6313,11 +6225,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6325,7 +6233,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6566,11 +6474,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6578,7 +6482,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6815,11 +6719,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6827,7 +6727,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7068,11 +6968,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7080,7 +6976,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7321,11 +7217,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7333,7 +7225,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7574,11 +7466,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7586,7 +7474,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7791,11 +7679,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7803,7 +7687,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8024,11 +7908,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8036,7 +7916,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8277,11 +8157,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8289,7 +8165,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8530,11 +8406,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8542,7 +8414,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8783,11 +8655,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8795,7 +8663,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9036,11 +8904,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9048,7 +8912,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9289,11 +9153,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9301,7 +9161,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9542,11 +9402,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9554,7 +9410,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9771,11 +9627,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9783,7 +9635,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10024,11 +9876,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10036,7 +9884,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10277,11 +10125,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10289,7 +10133,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10530,11 +10374,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10542,7 +10382,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10783,11 +10623,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10795,7 +10631,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11028,11 +10864,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11040,7 +10872,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11281,11 +11113,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11293,7 +11121,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11530,11 +11358,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11542,7 +11366,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11783,11 +11607,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11795,7 +11615,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12036,11 +11856,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12048,7 +11864,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12289,11 +12105,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12301,7 +12113,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12542,11 +12354,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12554,7 +12362,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12795,11 +12603,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12807,7 +12611,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13048,11 +12852,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13060,7 +12860,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13273,11 +13073,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13285,7 +13081,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13522,11 +13318,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13534,7 +13326,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13775,11 +13567,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13787,7 +13575,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14028,11 +13816,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14040,7 +13824,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14281,11 +14065,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14293,7 +14073,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14534,11 +14314,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14546,7 +14322,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14787,11 +14563,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14799,7 +14571,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15008,11 +14780,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -15020,7 +14788,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
